--- a/3학년 2학기/기인프/기인프 5반 좌석표 개선판.xlsx
+++ b/3학년 2학기/기인프/기인프 5반 좌석표 개선판.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\SOGANG\3학년 2학기\기인프\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06415130-6790-4E82-863F-221043590087}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8738D8-6B8E-4187-8BC7-96208416E069}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9564" xr2:uid="{127D69E5-7973-4135-B76A-078775FF16D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>교탁</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,11 +116,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이*석
-2026***0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>장*호
 2026***0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -188,11 +183,6 @@
   <si>
     <t>이*민
 2026***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>임*슬
-2026***3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -811,11 +801,11 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>1</v>
@@ -827,10 +817,10 @@
         <v>3</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N3" s="4"/>
     </row>
@@ -856,7 +846,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>5</v>
@@ -868,7 +858,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>8</v>
@@ -904,9 +894,7 @@
       <c r="L6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="6"/>
@@ -926,59 +914,57 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="7"/>
       <c r="D9" s="3"/>
       <c r="E9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2"/>
+      <c r="M9" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
@@ -995,66 +981,66 @@
     </row>
     <row r="11" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
